--- a/artfynd/A 35158-2022 artfynd.xlsx
+++ b/artfynd/A 35158-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35158-2022 artfynd.xlsx
+++ b/artfynd/A 35158-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102650297</v>
+        <v>106872950</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Änge, Risberget, Offerdal, Jmt</t>
+          <t>Kyrkberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457910.1993462131</v>
+        <v>457924</v>
       </c>
       <c r="R2" t="n">
-        <v>7038966.402941669</v>
+        <v>7038752</v>
       </c>
       <c r="S2" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,34 +765,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Moa Lönneborg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Moa Lönneborg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102650405</v>
+        <v>106872948</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,40 +794,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Änge, Risberget, Offerdal, Jmt</t>
+          <t>Kyrkberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457945.4728264888</v>
+        <v>457926</v>
       </c>
       <c r="R3" t="n">
-        <v>7038789.801547648</v>
+        <v>7038752</v>
       </c>
       <c r="S3" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,481 +873,21 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Moa Lönneborg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Moa Lönneborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>102650341</v>
-      </c>
-      <c r="B4" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>219795</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grönkulla</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Coeloglossum viride</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Änge, Risberget, Offerdal, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>457928.4691732268</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7038654.564104584</v>
-      </c>
-      <c r="S4" t="n">
-        <v>150</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>102650295</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Änge, Risberget, Offerdal, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>457910.1993462131</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7038966.402941669</v>
-      </c>
-      <c r="S5" t="n">
-        <v>125</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>106872950</v>
-      </c>
-      <c r="B6" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Kyrkberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>457924</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7038752</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Moa Lönneborg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Moa Lönneborg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>106872948</v>
-      </c>
-      <c r="B7" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Kyrkberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>457926</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7038752</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Moa Lönneborg</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Moa Lönneborg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35158-2022 artfynd.xlsx
+++ b/artfynd/A 35158-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106872950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106872948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>